--- a/frontend/public/templates/projects_template.xlsx
+++ b/frontend/public/templates/projects_template.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,11 @@
           <t>tags</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>track</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -523,6 +528,7 @@
           <t>NLP, Chatbot</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">

--- a/frontend/public/templates/projects_template.xlsx
+++ b/frontend/public/templates/projects_template.xlsx
@@ -471,34 +471,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>title *</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>description *</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>author *</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>telegram_contact</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tags</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Название *</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Описание *</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Автор *</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Телеграм</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Тематики</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>Трек</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,6 @@
           <t>NLP, Chatbot</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
